--- a/GameData/DataTables/Board/AnomalyTable.xlsx
+++ b/GameData/DataTables/Board/AnomalyTable.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,6 +478,11 @@
           <t>TapPeriod</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ExtraData</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -525,6 +530,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -570,6 +580,11 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>拍击后反转周期</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>逐项参数，k=v;k=v 分号分隔；空表示用代码默认值</t>
         </is>
       </c>
     </row>
@@ -589,16 +604,21 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Priority=10;Controllable=1</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -614,19 +634,24 @@
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>MaxExpansion=2</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -642,19 +667,24 @@
         <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>EchoQuota=3;Resettable=1;NoEchoOfEcho=1</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -670,19 +700,24 @@
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SuppressStoryNodes=0;Controllable=1</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -698,19 +733,24 @@
         <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>StepLength=1</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -726,10 +766,10 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>3</v>
@@ -738,7 +778,12 @@
         <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>RechargeAmount=1</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -754,19 +799,24 @@
         <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>MaxLayers=2;PerRoundTargets=1</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -782,19 +832,24 @@
         <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>2</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>FlipDegrees=180</t>
+        </is>
       </c>
     </row>
   </sheetData>
